--- a/รายได้-UFA66-20220228-20220306.xlsx
+++ b/รายได้-UFA66-20220228-20220306.xlsx
@@ -12471,32 +12471,1540 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>9457.05</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>3551</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>3551</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>10457</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>21761.15</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>3482</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>9946</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>9946</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>25243</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>10097</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>618.94</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>974</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>10223.28</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>3293</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>3183</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>-24831</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-101913</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-88396</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>-22099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>32024.52</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>6376</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>11689</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>10002</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>38400</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>15360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>69408.45</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>9636</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>26370</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>-141901</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-183045</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>-104000</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>-31200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>4164.62</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>4346</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>2186</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>-5406</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>8510</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>4408.17</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>2230</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>1583</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>-19347</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>-306416</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>-299777</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>-89933</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>1109.19</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>1542</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>552</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>-363</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>2651</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>66413.42</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>23513</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>20354</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>-8345</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>58144</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>17443</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>7626.81</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>-360</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>-6313</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>2473</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>3614.05</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>1534</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>1484</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>4618</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>15994.61</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>5903</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>5013</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>18004</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>7201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>7175.48</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>1484</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>2959</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>2959</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>8659</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>63630.82</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>40425</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>79170</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>-2885</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>104055</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>36419</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>21279.79</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>5261</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>8203</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>6997</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>26540</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>9289</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>1520.45</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>543</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>-2775</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>-17002</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>-15291</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>-6116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>48372.54</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>8383</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>23540</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>17115</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>56755</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>22702</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>-7012</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>-6925</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>-2770</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>-7236.06</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>829</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>-6961</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>-74878</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>-81285</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>-28449</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>2897.4</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>3449</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>1527</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>-9773</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>-3426</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>-1370</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>166.62</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>-1130</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>-963</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>-385</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>11410.37</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>735</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>5300</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>-18279</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>-72013</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>-59867</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>-23946</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>5404.54</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>1685</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>1410</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>-5658</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>7089</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>16324.31</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>6677</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>6679</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>-38112</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>-53203</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>-30201</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>-12080</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>438.84</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>156</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>156</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>-11743</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>-11275</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>-4510</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>-29781.56</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>2231</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>2263</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>-189497</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>-525699</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>-553249</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>-221299</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>5710.05</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1903</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>-11337</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>-40263</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>-34552</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>-13820</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>13495.97</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>19268</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>14385</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>-444049</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>-1027822</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>-995058</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>-447776</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>88349.52</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>17023</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>36842</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>15213</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>105372</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>42148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>4927.94</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>213</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1776</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>-9931</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>-4790</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>8834.94</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>12230</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>6514</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>-3468</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>-1908</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>19156</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>6704</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>-2457.55</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>-13909</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>-42599</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>-45056</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>-15769</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>538.1</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>384</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>-1848</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>-7508</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>-6585</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>-2304</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>21684.2</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>5250</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>8310</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>26934</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>9426</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>157</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>-422</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>-4048</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>-4039</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>-1413</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>2237.96</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>708</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>-90</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>-3322</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>-376</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>-131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>-15012.64</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>2451</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>442</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>-8813</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>-81895</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>-94456</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>-23614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>1098.43</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>402</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>402</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>1307</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>-2284.14</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>6146</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>5474</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>-4689</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>3861</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>21738.42</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>1466</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>9324</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>8505</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>-8214</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>14990</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>5996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>-1772.49</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>-1709</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>-598</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>137048.02</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>13411</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>24442</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>-6140</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>-83997</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>66462</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>23261</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>2726.5</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>1213</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>863</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>-1559</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>3939</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>60825.71</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>26083</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>25286</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>-54546</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>15279</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>6111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>56432.65</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>6452</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>18538</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>12869</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>-94126</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>-31241</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>-10934</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>24846.53</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>2758</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>8993</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>-119928</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>-92323</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>-36929</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>-91208.17</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>7186</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>-43350</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>-79208</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>-23762</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>1379.73</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>387</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>726</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>238</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>1766</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>121363.29</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>9197</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>38547</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>16567</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>-11742</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>118818</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>59409</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>3199.59</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>390</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>1561</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>1561</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>3589</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>14475.84</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>1327</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>6357</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>5910</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>-31736</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>-15933</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>-5576</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>15920.03</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>5650</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>12136</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>-204385</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>-457602</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>-436031</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>-152610</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>31598.04</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>33279</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>58419</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>-447000</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>-964530</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>-899652</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>-449826</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>-47.76</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>-1387</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>-1268</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>-507</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="0" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="0" t="n">
+      <c r="B59" s="0" t="n">
         <v>54619.04</v>
       </c>
-      <c r="C1" s="0" t="n">
+      <c r="C59" s="0" t="n">
         <v>1592</v>
       </c>
-      <c r="D1" s="0" t="n">
+      <c r="D59" s="0" t="n">
         <v>21422</v>
       </c>
-      <c r="E1" s="0" t="n">
+      <c r="E59" s="0" t="n">
         <v>6190</v>
       </c>
-      <c r="F1" s="0" t="n">
+      <c r="F59" s="0" t="n">
         <v>-28117</v>
       </c>
-      <c r="G1" s="0" t="n">
+      <c r="G59" s="0" t="n">
         <v>28094</v>
       </c>
-      <c r="H1" s="0" t="n">
+      <c r="H59" s="0" t="n">
         <v>11237</v>
       </c>
     </row>

--- a/รายได้-UFA66-20220228-20220306.xlsx
+++ b/รายได้-UFA66-20220228-20220306.xlsx
@@ -12592,7 +12592,7 @@
         <v>3183</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>-24831</v>
+        <v>611</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>-101913</v>
@@ -12618,7 +12618,7 @@
         <v>11689</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>10002</v>
+        <v>10173</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0</v>
@@ -12644,7 +12644,7 @@
         <v>26370</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>-141901</v>
+        <v>13823</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>-183045</v>
@@ -12670,7 +12670,7 @@
         <v>2186</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>-5406</v>
+        <v>2136</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0</v>
@@ -12696,7 +12696,7 @@
         <v>1583</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>-19347</v>
+        <v>0</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>-306416</v>
@@ -12722,7 +12722,7 @@
         <v>552</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>-363</v>
+        <v>552</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
         <v>1100</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>-360</v>
+        <v>555</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>-6313</v>
@@ -12826,7 +12826,7 @@
         <v>5903</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>5013</v>
+        <v>5784</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0</v>
@@ -12878,7 +12878,7 @@
         <v>79170</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>-2885</v>
+        <v>75958</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0</v>
@@ -12904,7 +12904,7 @@
         <v>8203</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>6997</v>
+        <v>7359</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>0</v>
@@ -12930,7 +12930,7 @@
         <v>543</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>-2775</v>
+        <v>514</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>-17002</v>
@@ -12956,7 +12956,7 @@
         <v>23540</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>17115</v>
+        <v>19225</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>0</v>
@@ -13008,7 +13008,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>-6961</v>
+        <v>16</v>
       </c>
       <c r="F21" s="0" t="n">
         <v>-74878</v>
@@ -13086,7 +13086,7 @@
         <v>5300</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>-18279</v>
+        <v>0</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>-72013</v>
@@ -13112,7 +13112,7 @@
         <v>1410</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>-5658</v>
+        <v>541</v>
       </c>
       <c r="F25" s="0" t="n">
         <v>0</v>
@@ -13138,7 +13138,7 @@
         <v>6679</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>-38112</v>
+        <v>6389</v>
       </c>
       <c r="F26" s="0" t="n">
         <v>-53203</v>
@@ -13190,7 +13190,7 @@
         <v>2263</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>-189497</v>
+        <v>183</v>
       </c>
       <c r="F28" s="0" t="n">
         <v>-525699</v>
@@ -13216,7 +13216,7 @@
         <v>1903</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>-11337</v>
+        <v>0</v>
       </c>
       <c r="F29" s="0" t="n">
         <v>-40263</v>
@@ -13242,7 +13242,7 @@
         <v>14385</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>-444049</v>
+        <v>11042</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>-1027822</v>
@@ -13268,7 +13268,7 @@
         <v>36842</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>15213</v>
+        <v>33033</v>
       </c>
       <c r="F31" s="0" t="n">
         <v>0</v>
@@ -13320,7 +13320,7 @@
         <v>6514</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>-3468</v>
+        <v>5386</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>-1908</v>
@@ -13346,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>-13909</v>
+        <v>0</v>
       </c>
       <c r="F34" s="0" t="n">
         <v>-42599</v>
@@ -13372,7 +13372,7 @@
         <v>169</v>
       </c>
       <c r="E35" s="0" t="n">
-        <v>-1848</v>
+        <v>0</v>
       </c>
       <c r="F35" s="0" t="n">
         <v>-7508</v>
@@ -13398,7 +13398,7 @@
         <v>8310</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>2950</v>
+        <v>7887</v>
       </c>
       <c r="F36" s="0" t="n">
         <v>0</v>
@@ -13450,7 +13450,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="0" t="n">
-        <v>-422</v>
+        <v>0</v>
       </c>
       <c r="F38" s="0" t="n">
         <v>-4048</v>
@@ -13476,7 +13476,7 @@
         <v>2396</v>
       </c>
       <c r="E39" s="0" t="n">
-        <v>-90</v>
+        <v>2376</v>
       </c>
       <c r="F39" s="0" t="n">
         <v>-3322</v>
@@ -13502,7 +13502,7 @@
         <v>442</v>
       </c>
       <c r="E40" s="0" t="n">
-        <v>-8813</v>
+        <v>0</v>
       </c>
       <c r="F40" s="0" t="n">
         <v>-81895</v>
@@ -13554,7 +13554,7 @@
         <v>5474</v>
       </c>
       <c r="E42" s="0" t="n">
-        <v>-4689</v>
+        <v>3677</v>
       </c>
       <c r="F42" s="0" t="n">
         <v>0</v>
@@ -13580,7 +13580,7 @@
         <v>9324</v>
       </c>
       <c r="E43" s="0" t="n">
-        <v>8505</v>
+        <v>8938</v>
       </c>
       <c r="F43" s="0" t="n">
         <v>-8214</v>
@@ -13606,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="0" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="F44" s="0" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>24442</v>
       </c>
       <c r="E45" s="0" t="n">
-        <v>-6140</v>
+        <v>3387</v>
       </c>
       <c r="F45" s="0" t="n">
         <v>-83997</v>
@@ -13658,7 +13658,7 @@
         <v>863</v>
       </c>
       <c r="E46" s="0" t="n">
-        <v>-1559</v>
+        <v>732</v>
       </c>
       <c r="F46" s="0" t="n">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>26083</v>
       </c>
       <c r="E47" s="0" t="n">
-        <v>25286</v>
+        <v>25997</v>
       </c>
       <c r="F47" s="0" t="n">
         <v>-54546</v>
@@ -13710,7 +13710,7 @@
         <v>18538</v>
       </c>
       <c r="E48" s="0" t="n">
-        <v>12869</v>
+        <v>14493</v>
       </c>
       <c r="F48" s="0" t="n">
         <v>-94126</v>
@@ -13753,7 +13753,7 @@
         <v>248</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>-91208.17</v>
+        <v>-91208.16</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>12000</v>
@@ -13762,7 +13762,7 @@
         <v>7186</v>
       </c>
       <c r="E50" s="0" t="n">
-        <v>-43350</v>
+        <v>6073</v>
       </c>
       <c r="F50" s="0" t="n">
         <v>0</v>
@@ -13788,7 +13788,7 @@
         <v>726</v>
       </c>
       <c r="E51" s="0" t="n">
-        <v>238</v>
+        <v>726</v>
       </c>
       <c r="F51" s="0" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>38547</v>
       </c>
       <c r="E52" s="0" t="n">
-        <v>16567</v>
+        <v>21543</v>
       </c>
       <c r="F52" s="0" t="n">
         <v>-11742</v>
@@ -13892,7 +13892,7 @@
         <v>12136</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>-204385</v>
+        <v>11730</v>
       </c>
       <c r="F55" s="0" t="n">
         <v>-457602</v>
@@ -13918,7 +13918,7 @@
         <v>58419</v>
       </c>
       <c r="E56" s="0" t="n">
-        <v>-447000</v>
+        <v>42683</v>
       </c>
       <c r="F56" s="0" t="n">
         <v>-964530</v>
@@ -13970,7 +13970,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="0" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F58" s="0" t="n">
         <v>-1387</v>
@@ -13996,7 +13996,7 @@
         <v>21422</v>
       </c>
       <c r="E59" s="0" t="n">
-        <v>6190</v>
+        <v>10416</v>
       </c>
       <c r="F59" s="0" t="n">
         <v>-28117</v>

--- a/รายได้-UFA66-20220228-20220306.xlsx
+++ b/รายได้-UFA66-20220228-20220306.xlsx
@@ -12505,25 +12505,25 @@
         <v>14</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>9457.05</v>
+        <v>9457</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>3551</v>
+        <v>-3551</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>3551</v>
+        <v>-3551</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>10457</v>
+        <v>4906</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>3137</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -12531,25 +12531,25 @@
         <v>16</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>21761.15</v>
+        <v>21761</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>3482</v>
+        <v>-3482</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>9946</v>
+        <v>-9946</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>9946</v>
+        <v>-9946</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>25243</v>
+        <v>8333</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>10097</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -12557,10 +12557,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>618.94</v>
+        <v>618</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>356</v>
+        <v>-356</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>0</v>
@@ -12572,10 +12572,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>974</v>
+        <v>262</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>389</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -12583,25 +12583,25 @@
         <v>22</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>10223.28</v>
+        <v>10223</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>3293</v>
+        <v>-3293</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>3183</v>
+        <v>-3183</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>611</v>
+        <v>-611</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>-101913</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>-88396</v>
+        <v>105660</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>-22099</v>
+        <v>26415</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -12609,25 +12609,25 @@
         <v>26</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>32024.52</v>
+        <v>32024</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>6376</v>
+        <v>-6376</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>11689</v>
+        <v>-11689</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>10173</v>
+        <v>-10173</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>38400</v>
+        <v>15475</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>15360</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -12635,25 +12635,25 @@
         <v>32</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>69408.45</v>
+        <v>69408</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>9636</v>
+        <v>-9636</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>26370</v>
+        <v>-26370</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>13823</v>
+        <v>-13823</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>-183045</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>-104000</v>
+        <v>216447</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>-31200</v>
+        <v>64934</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -12661,25 +12661,25 @@
         <v>38</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>4164.62</v>
+        <v>4164</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>4346</v>
+        <v>-4346</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>2186</v>
+        <v>-2186</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>2136</v>
+        <v>-2136</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>8510</v>
+        <v>-2368</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>2553</v>
+        <v>-710</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -12687,13 +12687,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>4408.17</v>
+        <v>4408</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>2230</v>
+        <v>-2230</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>1583</v>
+        <v>-1583</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>0</v>
@@ -12702,10 +12702,10 @@
         <v>-306416</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>-299777</v>
+        <v>307011</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>-89933</v>
+        <v>92103</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -12713,25 +12713,25 @@
         <v>46</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>1109.19</v>
+        <v>1109</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>1542</v>
+        <v>-1542</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>552</v>
+        <v>-552</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>552</v>
+        <v>-552</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>2651</v>
+        <v>-985</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>927</v>
+        <v>-344</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -12739,25 +12739,25 @@
         <v>49</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>66413.42</v>
+        <v>66413</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>76</v>
+        <v>-76</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>23513</v>
+        <v>-23513</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>20354</v>
+        <v>-20354</v>
       </c>
       <c r="F11" s="0" t="n">
         <v>-8345</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>58144</v>
+        <v>51169</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>17443</v>
+        <v>15350</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -12765,25 +12765,25 @@
         <v>52</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>7626.81</v>
+        <v>7626</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>1160</v>
+        <v>-1160</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>1100</v>
+        <v>-1100</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>555</v>
+        <v>-555</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>-6313</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>2473</v>
+        <v>11679</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>865</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -12791,25 +12791,25 @@
         <v>58</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>3614.05</v>
+        <v>3614</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>1004</v>
+        <v>-1004</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>1534</v>
+        <v>-1534</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>1484</v>
+        <v>-1484</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>4618</v>
+        <v>1076</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>1616</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -12817,25 +12817,25 @@
         <v>61</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>15994.61</v>
+        <v>15994</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>2010</v>
+        <v>-2010</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>5903</v>
+        <v>-5903</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>5784</v>
+        <v>-5784</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>18004</v>
+        <v>8081</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>7201</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -12843,25 +12843,25 @@
         <v>66</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>7175.48</v>
+        <v>7175</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>1484</v>
+        <v>-1484</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>2959</v>
+        <v>-2959</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>2959</v>
+        <v>-2959</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>8659</v>
+        <v>2732</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>3030</v>
+        <v>956</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -12869,25 +12869,25 @@
         <v>68</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>63630.82</v>
+        <v>63630</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>40425</v>
+        <v>-40425</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>79170</v>
+        <v>-79170</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>75958</v>
+        <v>-75958</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>104055</v>
+        <v>-55965</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>36419</v>
+        <v>-19587</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -12895,25 +12895,25 @@
         <v>80</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>21279.79</v>
+        <v>21279</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>5261</v>
+        <v>-5261</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>8203</v>
+        <v>-8203</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>7359</v>
+        <v>-7359</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>26540</v>
+        <v>7815</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>9289</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -12921,25 +12921,25 @@
         <v>86</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>1520.45</v>
+        <v>1520</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>190</v>
+        <v>-190</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>543</v>
+        <v>-543</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>514</v>
+        <v>-514</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>-17002</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>-15291</v>
+        <v>17789</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>-6116</v>
+        <v>7115</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -12947,25 +12947,25 @@
         <v>89</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>48372.54</v>
+        <v>48372</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>8383</v>
+        <v>-8383</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>23540</v>
+        <v>-23540</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>19225</v>
+        <v>-19225</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>56755</v>
+        <v>16449</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>22702</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -12973,25 +12973,25 @@
         <v>100</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>37.76</v>
+        <v>37</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>49</v>
+        <v>-49</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>-7012</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>-6925</v>
+        <v>6986</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>-2770</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -12999,25 +12999,25 @@
         <v>102</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>-7236.06</v>
+        <v>-7236</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>829</v>
+        <v>-829</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>16</v>
+        <v>-16</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>16</v>
+        <v>-16</v>
       </c>
       <c r="F21" s="0" t="n">
         <v>-74878</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>-81285</v>
+        <v>66797</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>-28449</v>
+        <v>23378</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -13025,25 +13025,25 @@
         <v>105</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>2897.4</v>
+        <v>2897</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>3449</v>
+        <v>-3449</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>1527</v>
+        <v>-1527</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>1527</v>
+        <v>-1527</v>
       </c>
       <c r="F22" s="0" t="n">
         <v>-9773</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>-3426</v>
+        <v>7694</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>-1370</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -13051,7 +13051,7 @@
         <v>107</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>166.62</v>
+        <v>166</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>0</v>
@@ -13063,13 +13063,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>-1130</v>
+        <v>0</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>-963</v>
+        <v>166</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>-385</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -13077,13 +13077,13 @@
         <v>109</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>11410.37</v>
+        <v>11410</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>735</v>
+        <v>-735</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>5300</v>
+        <v>-5300</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>-72013</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>-59867</v>
+        <v>77388</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>-23946</v>
+        <v>30955</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -13103,25 +13103,25 @@
         <v>111</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>5404.54</v>
+        <v>5404</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>1685</v>
+        <v>-1685</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>1410</v>
+        <v>-1410</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>541</v>
+        <v>-541</v>
       </c>
       <c r="F25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>7089</v>
+        <v>2309</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>2126</v>
+        <v>692</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -13129,25 +13129,25 @@
         <v>114</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>16324.31</v>
+        <v>16324</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>6677</v>
+        <v>-6677</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>6679</v>
+        <v>-6679</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>6389</v>
+        <v>-6389</v>
       </c>
       <c r="F26" s="0" t="n">
         <v>-53203</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>-30201</v>
+        <v>56461</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>-12080</v>
+        <v>22584</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -13155,25 +13155,25 @@
         <v>120</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>438.84</v>
+        <v>438</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>29</v>
+        <v>-29</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>156</v>
+        <v>-156</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>156</v>
+        <v>-156</v>
       </c>
       <c r="F27" s="0" t="n">
         <v>-11743</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>-11275</v>
+        <v>11996</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>-4510</v>
+        <v>4798</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -13181,25 +13181,25 @@
         <v>122</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>-29781.56</v>
+        <v>-29781</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>2231</v>
+        <v>-2231</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>2263</v>
+        <v>-2263</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>183</v>
+        <v>-183</v>
       </c>
       <c r="F28" s="0" t="n">
         <v>-525699</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>-553249</v>
+        <v>491424</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>-221299</v>
+        <v>196569</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -13207,13 +13207,13 @@
         <v>129</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>5710.05</v>
+        <v>5710</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>1903</v>
+        <v>-1903</v>
       </c>
       <c r="E29" s="0" t="n">
         <v>0</v>
@@ -13222,10 +13222,10 @@
         <v>-40263</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>-34552</v>
+        <v>44070</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>-13820</v>
+        <v>17628</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -13233,25 +13233,25 @@
         <v>131</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>13495.97</v>
+        <v>13495</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>19268</v>
+        <v>-19268</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>14385</v>
+        <v>-14385</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>11042</v>
+        <v>-11042</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>-1027822</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>-995058</v>
+        <v>1007664</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>-447776</v>
+        <v>453448</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -13259,25 +13259,25 @@
         <v>145</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>88349.52</v>
+        <v>88349</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>17023</v>
+        <v>-17023</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>36842</v>
+        <v>-36842</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>33033</v>
+        <v>-33033</v>
       </c>
       <c r="F31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>105372</v>
+        <v>34484</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>42148</v>
+        <v>13793</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -13285,22 +13285,22 @@
         <v>162</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>4927.94</v>
+        <v>4927</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>213</v>
+        <v>-213</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>1776</v>
+        <v>-1776</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>247</v>
+        <v>-247</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>-9931</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>-4790</v>
+        <v>12869</v>
       </c>
       <c r="H32" s="0" t="n">
         <v>0</v>
@@ -13311,25 +13311,25 @@
         <v>164</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>8834.94</v>
+        <v>8834</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>12230</v>
+        <v>-12230</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>6514</v>
+        <v>-6514</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>5386</v>
+        <v>-5386</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>-1908</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>19156</v>
+        <v>-8002</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>6704</v>
+        <v>-2800</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -13337,7 +13337,7 @@
         <v>176</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>-2457.55</v>
+        <v>-2457</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>0</v>
@@ -13352,10 +13352,10 @@
         <v>-42599</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>-45056</v>
+        <v>40142</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>-15769</v>
+        <v>14049</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -13363,13 +13363,13 @@
         <v>178</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>538.1</v>
+        <v>538</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>384</v>
+        <v>-384</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>169</v>
+        <v>-169</v>
       </c>
       <c r="E35" s="0" t="n">
         <v>0</v>
@@ -13378,10 +13378,10 @@
         <v>-7508</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>-6585</v>
+        <v>7493</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>-2304</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -13389,25 +13389,25 @@
         <v>180</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>21684.2</v>
+        <v>21684</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>5250</v>
+        <v>-5250</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>8310</v>
+        <v>-8310</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>7887</v>
+        <v>-7887</v>
       </c>
       <c r="F36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="0" t="n">
-        <v>26934</v>
+        <v>8124</v>
       </c>
       <c r="H36" s="0" t="n">
-        <v>9426</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -13415,25 +13415,25 @@
         <v>188</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>51</v>
+        <v>-51</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="F37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="0" t="n">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -13441,7 +13441,7 @@
         <v>190</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>0</v>
@@ -13456,10 +13456,10 @@
         <v>-4048</v>
       </c>
       <c r="G38" s="0" t="n">
-        <v>-4039</v>
+        <v>4056</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>-1413</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -13467,25 +13467,25 @@
         <v>192</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>2237.96</v>
+        <v>2237</v>
       </c>
       <c r="C39" s="0" t="n">
-        <v>708</v>
+        <v>-708</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>2396</v>
+        <v>-2396</v>
       </c>
       <c r="E39" s="0" t="n">
-        <v>2376</v>
+        <v>-2376</v>
       </c>
       <c r="F39" s="0" t="n">
         <v>-3322</v>
       </c>
       <c r="G39" s="0" t="n">
-        <v>-376</v>
+        <v>2455</v>
       </c>
       <c r="H39" s="0" t="n">
-        <v>-131</v>
+        <v>859</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -13493,13 +13493,13 @@
         <v>197</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>-15012.64</v>
+        <v>-15012</v>
       </c>
       <c r="C40" s="0" t="n">
-        <v>2451</v>
+        <v>-2451</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>442</v>
+        <v>-442</v>
       </c>
       <c r="E40" s="0" t="n">
         <v>0</v>
@@ -13508,10 +13508,10 @@
         <v>-81895</v>
       </c>
       <c r="G40" s="0" t="n">
-        <v>-94456</v>
+        <v>63990</v>
       </c>
       <c r="H40" s="0" t="n">
-        <v>-23614</v>
+        <v>15997</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -13519,25 +13519,25 @@
         <v>201</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>1098.43</v>
+        <v>1098</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>209</v>
+        <v>-209</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>402</v>
+        <v>-402</v>
       </c>
       <c r="E41" s="0" t="n">
-        <v>402</v>
+        <v>-402</v>
       </c>
       <c r="F41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="0" t="n">
-        <v>1307</v>
+        <v>487</v>
       </c>
       <c r="H41" s="0" t="n">
-        <v>392</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -13545,25 +13545,25 @@
         <v>203</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>-2284.14</v>
+        <v>-2284</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>6146</v>
+        <v>-6146</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>5474</v>
+        <v>-5474</v>
       </c>
       <c r="E42" s="0" t="n">
-        <v>3677</v>
+        <v>-3677</v>
       </c>
       <c r="F42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="0" t="n">
-        <v>3861</v>
+        <v>-13904</v>
       </c>
       <c r="H42" s="0" t="n">
-        <v>1351</v>
+        <v>-4866</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -13571,25 +13571,25 @@
         <v>213</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>21738.42</v>
+        <v>21738</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>1466</v>
+        <v>-1466</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>9324</v>
+        <v>-9324</v>
       </c>
       <c r="E43" s="0" t="n">
-        <v>8938</v>
+        <v>-8938</v>
       </c>
       <c r="F43" s="0" t="n">
         <v>-8214</v>
       </c>
       <c r="G43" s="0" t="n">
-        <v>14990</v>
+        <v>19162</v>
       </c>
       <c r="H43" s="0" t="n">
-        <v>5996</v>
+        <v>7664</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -13597,10 +13597,10 @@
         <v>216</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>-1772.49</v>
+        <v>-1772</v>
       </c>
       <c r="C44" s="0" t="n">
-        <v>63</v>
+        <v>-63</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>0</v>
@@ -13612,10 +13612,10 @@
         <v>0</v>
       </c>
       <c r="G44" s="0" t="n">
-        <v>-1709</v>
+        <v>-1835</v>
       </c>
       <c r="H44" s="0" t="n">
-        <v>-598</v>
+        <v>-642</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -13623,25 +13623,25 @@
         <v>218</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>137048.02</v>
+        <v>137048</v>
       </c>
       <c r="C45" s="0" t="n">
-        <v>13411</v>
+        <v>-13411</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>24442</v>
+        <v>-24442</v>
       </c>
       <c r="E45" s="0" t="n">
-        <v>3387</v>
+        <v>-3387</v>
       </c>
       <c r="F45" s="0" t="n">
         <v>-83997</v>
       </c>
       <c r="G45" s="0" t="n">
-        <v>66462</v>
+        <v>183192</v>
       </c>
       <c r="H45" s="0" t="n">
-        <v>23261</v>
+        <v>64117</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -13649,25 +13649,25 @@
         <v>224</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>2726.5</v>
+        <v>2726</v>
       </c>
       <c r="C46" s="0" t="n">
-        <v>1213</v>
+        <v>-1213</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>863</v>
+        <v>-863</v>
       </c>
       <c r="E46" s="0" t="n">
-        <v>732</v>
+        <v>-732</v>
       </c>
       <c r="F46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="0" t="n">
-        <v>3939</v>
+        <v>650</v>
       </c>
       <c r="H46" s="0" t="n">
-        <v>1181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -13675,25 +13675,25 @@
         <v>227</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>60825.71</v>
+        <v>60825</v>
       </c>
       <c r="C47" s="0" t="n">
-        <v>9000</v>
+        <v>-9000</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>26083</v>
+        <v>-26083</v>
       </c>
       <c r="E47" s="0" t="n">
-        <v>25997</v>
+        <v>-25997</v>
       </c>
       <c r="F47" s="0" t="n">
         <v>-54546</v>
       </c>
       <c r="G47" s="0" t="n">
-        <v>15279</v>
+        <v>80288</v>
       </c>
       <c r="H47" s="0" t="n">
-        <v>6111</v>
+        <v>32115</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -13701,25 +13701,25 @@
         <v>236</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>56432.65</v>
+        <v>56432</v>
       </c>
       <c r="C48" s="0" t="n">
-        <v>6452</v>
+        <v>-6452</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>18538</v>
+        <v>-18538</v>
       </c>
       <c r="E48" s="0" t="n">
-        <v>14493</v>
+        <v>-14493</v>
       </c>
       <c r="F48" s="0" t="n">
         <v>-94126</v>
       </c>
       <c r="G48" s="0" t="n">
-        <v>-31241</v>
+        <v>125568</v>
       </c>
       <c r="H48" s="0" t="n">
-        <v>-10934</v>
+        <v>43948</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -13727,25 +13727,25 @@
         <v>245</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>24846.53</v>
+        <v>24846</v>
       </c>
       <c r="C49" s="0" t="n">
-        <v>2758</v>
+        <v>-2758</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>8993</v>
+        <v>-8993</v>
       </c>
       <c r="E49" s="0" t="n">
-        <v>6436</v>
+        <v>-6436</v>
       </c>
       <c r="F49" s="0" t="n">
         <v>-119928</v>
       </c>
       <c r="G49" s="0" t="n">
-        <v>-92323</v>
+        <v>133023</v>
       </c>
       <c r="H49" s="0" t="n">
-        <v>-36929</v>
+        <v>53209</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -13753,25 +13753,25 @@
         <v>248</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>-91208.16</v>
+        <v>-91208</v>
       </c>
       <c r="C50" s="0" t="n">
-        <v>12000</v>
+        <v>-12000</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>7186</v>
+        <v>-7186</v>
       </c>
       <c r="E50" s="0" t="n">
-        <v>6073</v>
+        <v>-6073</v>
       </c>
       <c r="F50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="0" t="n">
-        <v>-79208</v>
+        <v>-110394</v>
       </c>
       <c r="H50" s="0" t="n">
-        <v>-23762</v>
+        <v>-33118</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -13779,25 +13779,25 @@
         <v>260</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>1379.73</v>
+        <v>1379</v>
       </c>
       <c r="C51" s="0" t="n">
-        <v>387</v>
+        <v>-387</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>726</v>
+        <v>-726</v>
       </c>
       <c r="E51" s="0" t="n">
-        <v>726</v>
+        <v>-726</v>
       </c>
       <c r="F51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="0" t="n">
-        <v>1766</v>
+        <v>266</v>
       </c>
       <c r="H51" s="0" t="n">
-        <v>529</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -13805,25 +13805,25 @@
         <v>264</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>121363.29</v>
+        <v>121363</v>
       </c>
       <c r="C52" s="0" t="n">
-        <v>9197</v>
+        <v>-9197</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>38547</v>
+        <v>-38547</v>
       </c>
       <c r="E52" s="0" t="n">
-        <v>21543</v>
+        <v>-21543</v>
       </c>
       <c r="F52" s="0" t="n">
         <v>-11742</v>
       </c>
       <c r="G52" s="0" t="n">
-        <v>118818</v>
+        <v>85361</v>
       </c>
       <c r="H52" s="0" t="n">
-        <v>59409</v>
+        <v>42680</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -13831,25 +13831,25 @@
         <v>280</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>3199.59</v>
+        <v>3199</v>
       </c>
       <c r="C53" s="0" t="n">
-        <v>390</v>
+        <v>-390</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>1561</v>
+        <v>-1561</v>
       </c>
       <c r="E53" s="0" t="n">
-        <v>1561</v>
+        <v>-1561</v>
       </c>
       <c r="F53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="0" t="n">
-        <v>3589</v>
+        <v>1248</v>
       </c>
       <c r="H53" s="0" t="n">
-        <v>1256</v>
+        <v>436</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -13857,25 +13857,25 @@
         <v>284</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>14475.84</v>
+        <v>14475</v>
       </c>
       <c r="C54" s="0" t="n">
-        <v>1327</v>
+        <v>-1327</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>6357</v>
+        <v>-6357</v>
       </c>
       <c r="E54" s="0" t="n">
-        <v>5910</v>
+        <v>-5910</v>
       </c>
       <c r="F54" s="0" t="n">
         <v>-31736</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>-15933</v>
+        <v>38527</v>
       </c>
       <c r="H54" s="0" t="n">
-        <v>-5576</v>
+        <v>13484</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -13883,25 +13883,25 @@
         <v>286</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>15920.03</v>
+        <v>15920</v>
       </c>
       <c r="C55" s="0" t="n">
-        <v>5650</v>
+        <v>-5650</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>12136</v>
+        <v>-12136</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>11730</v>
+        <v>-11730</v>
       </c>
       <c r="F55" s="0" t="n">
         <v>-457602</v>
       </c>
       <c r="G55" s="0" t="n">
-        <v>-436031</v>
+        <v>455736</v>
       </c>
       <c r="H55" s="0" t="n">
-        <v>-152610</v>
+        <v>159507</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -13909,25 +13909,25 @@
         <v>297</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>31598.04</v>
+        <v>31598</v>
       </c>
       <c r="C56" s="0" t="n">
-        <v>33279</v>
+        <v>-33279</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>58419</v>
+        <v>-58419</v>
       </c>
       <c r="E56" s="0" t="n">
-        <v>42683</v>
+        <v>-42683</v>
       </c>
       <c r="F56" s="0" t="n">
         <v>-964530</v>
       </c>
       <c r="G56" s="0" t="n">
-        <v>-899652</v>
+        <v>904430</v>
       </c>
       <c r="H56" s="0" t="n">
-        <v>-449826</v>
+        <v>452215</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -13935,25 +13935,25 @@
         <v>320</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>39.24</v>
+        <v>39</v>
       </c>
       <c r="C57" s="0" t="n">
-        <v>48</v>
+        <v>-48</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>12</v>
+        <v>-12</v>
       </c>
       <c r="E57" s="0" t="n">
-        <v>12</v>
+        <v>-12</v>
       </c>
       <c r="F57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="0" t="n">
-        <v>87</v>
+        <v>-21</v>
       </c>
       <c r="H57" s="0" t="n">
-        <v>30</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -13961,10 +13961,10 @@
         <v>322</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>-47.76</v>
+        <v>-47</v>
       </c>
       <c r="C58" s="0" t="n">
-        <v>166</v>
+        <v>-166</v>
       </c>
       <c r="D58" s="0" t="n">
         <v>0</v>
@@ -13976,10 +13976,10 @@
         <v>-1387</v>
       </c>
       <c r="G58" s="0" t="n">
-        <v>-1268</v>
+        <v>1174</v>
       </c>
       <c r="H58" s="0" t="n">
-        <v>-507</v>
+        <v>469</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -13987,25 +13987,25 @@
         <v>324</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>54619.04</v>
+        <v>54619</v>
       </c>
       <c r="C59" s="0" t="n">
-        <v>1592</v>
+        <v>-1592</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>21422</v>
+        <v>-21422</v>
       </c>
       <c r="E59" s="0" t="n">
-        <v>10416</v>
+        <v>-10416</v>
       </c>
       <c r="F59" s="0" t="n">
         <v>-28117</v>
       </c>
       <c r="G59" s="0" t="n">
-        <v>28094</v>
+        <v>59722</v>
       </c>
       <c r="H59" s="0" t="n">
-        <v>11237</v>
+        <v>23888</v>
       </c>
     </row>
   </sheetData>

--- a/รายได้-UFA66-20220228-20220306.xlsx
+++ b/รายได้-UFA66-20220228-20220306.xlsx
@@ -12598,10 +12598,10 @@
         <v>-101913</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>105660</v>
+        <v>-98166</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>26415</v>
+        <v>-24541</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -12650,10 +12650,10 @@
         <v>-183045</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>216447</v>
+        <v>-149643</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>64934</v>
+        <v>-44892</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -12702,10 +12702,10 @@
         <v>-306416</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>307011</v>
+        <v>-305821</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>92103</v>
+        <v>-91746</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -12754,10 +12754,10 @@
         <v>-8345</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>51169</v>
+        <v>34479</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>15350</v>
+        <v>10343</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -12780,10 +12780,10 @@
         <v>-6313</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>11679</v>
+        <v>-947</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>4087</v>
+        <v>-331</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -12936,10 +12936,10 @@
         <v>-17002</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>17789</v>
+        <v>-16215</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>7115</v>
+        <v>-6486</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -12988,10 +12988,10 @@
         <v>-7012</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>6986</v>
+        <v>-7038</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>2794</v>
+        <v>-2815</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -13014,10 +13014,10 @@
         <v>-74878</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>66797</v>
+        <v>-82959</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>23378</v>
+        <v>-29035</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -13040,10 +13040,10 @@
         <v>-9773</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>7694</v>
+        <v>-11852</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>3077</v>
+        <v>-4740</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -13092,10 +13092,10 @@
         <v>-72013</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>77388</v>
+        <v>-66638</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>30955</v>
+        <v>-26655</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -13144,10 +13144,10 @@
         <v>-53203</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>56461</v>
+        <v>-49945</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>22584</v>
+        <v>-19978</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -13170,10 +13170,10 @@
         <v>-11743</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>11996</v>
+        <v>-11490</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>4798</v>
+        <v>-4596</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -13196,10 +13196,10 @@
         <v>-525699</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>491424</v>
+        <v>-559974</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>196569</v>
+        <v>-223989</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -13222,10 +13222,10 @@
         <v>-40263</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>44070</v>
+        <v>-36456</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>17628</v>
+        <v>-14582</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -13248,10 +13248,10 @@
         <v>-1027822</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>1007664</v>
+        <v>-1047980</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>453448</v>
+        <v>-471591</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -13300,7 +13300,7 @@
         <v>-9931</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>12869</v>
+        <v>-6993</v>
       </c>
       <c r="H32" s="0" t="n">
         <v>0</v>
@@ -13326,10 +13326,10 @@
         <v>-1908</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>-8002</v>
+        <v>-11818</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>-2800</v>
+        <v>-4136</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -13352,10 +13352,10 @@
         <v>-42599</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>40142</v>
+        <v>-45056</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>14049</v>
+        <v>-15769</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -13378,10 +13378,10 @@
         <v>-7508</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>7493</v>
+        <v>-7523</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>2622</v>
+        <v>-2633</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -13456,10 +13456,10 @@
         <v>-4048</v>
       </c>
       <c r="G38" s="0" t="n">
-        <v>4056</v>
+        <v>-4040</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>1419</v>
+        <v>-1414</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -13482,10 +13482,10 @@
         <v>-3322</v>
       </c>
       <c r="G39" s="0" t="n">
-        <v>2455</v>
+        <v>-4189</v>
       </c>
       <c r="H39" s="0" t="n">
-        <v>859</v>
+        <v>-1466</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -13508,10 +13508,10 @@
         <v>-81895</v>
       </c>
       <c r="G40" s="0" t="n">
-        <v>63990</v>
+        <v>-99800</v>
       </c>
       <c r="H40" s="0" t="n">
-        <v>15997</v>
+        <v>-24950</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -13586,10 +13586,10 @@
         <v>-8214</v>
       </c>
       <c r="G43" s="0" t="n">
-        <v>19162</v>
+        <v>2734</v>
       </c>
       <c r="H43" s="0" t="n">
-        <v>7664</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -13638,10 +13638,10 @@
         <v>-83997</v>
       </c>
       <c r="G45" s="0" t="n">
-        <v>183192</v>
+        <v>15198</v>
       </c>
       <c r="H45" s="0" t="n">
-        <v>64117</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -13690,10 +13690,10 @@
         <v>-54546</v>
       </c>
       <c r="G47" s="0" t="n">
-        <v>80288</v>
+        <v>-28804</v>
       </c>
       <c r="H47" s="0" t="n">
-        <v>32115</v>
+        <v>-11521</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -13716,10 +13716,10 @@
         <v>-94126</v>
       </c>
       <c r="G48" s="0" t="n">
-        <v>125568</v>
+        <v>-62684</v>
       </c>
       <c r="H48" s="0" t="n">
-        <v>43948</v>
+        <v>-21939</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -13742,10 +13742,10 @@
         <v>-119928</v>
       </c>
       <c r="G49" s="0" t="n">
-        <v>133023</v>
+        <v>-106833</v>
       </c>
       <c r="H49" s="0" t="n">
-        <v>53209</v>
+        <v>-42733</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -13820,10 +13820,10 @@
         <v>-11742</v>
       </c>
       <c r="G52" s="0" t="n">
-        <v>85361</v>
+        <v>61877</v>
       </c>
       <c r="H52" s="0" t="n">
-        <v>42680</v>
+        <v>30938</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -13872,10 +13872,10 @@
         <v>-31736</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>38527</v>
+        <v>-24945</v>
       </c>
       <c r="H54" s="0" t="n">
-        <v>13484</v>
+        <v>-8730</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -13898,10 +13898,10 @@
         <v>-457602</v>
       </c>
       <c r="G55" s="0" t="n">
-        <v>455736</v>
+        <v>-459468</v>
       </c>
       <c r="H55" s="0" t="n">
-        <v>159507</v>
+        <v>-160813</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -13924,10 +13924,10 @@
         <v>-964530</v>
       </c>
       <c r="G56" s="0" t="n">
-        <v>904430</v>
+        <v>-1024630</v>
       </c>
       <c r="H56" s="0" t="n">
-        <v>452215</v>
+        <v>-512315</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -13976,10 +13976,10 @@
         <v>-1387</v>
       </c>
       <c r="G58" s="0" t="n">
-        <v>1174</v>
+        <v>-1600</v>
       </c>
       <c r="H58" s="0" t="n">
-        <v>469</v>
+        <v>-640</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -14002,10 +14002,10 @@
         <v>-28117</v>
       </c>
       <c r="G59" s="0" t="n">
-        <v>59722</v>
+        <v>3488</v>
       </c>
       <c r="H59" s="0" t="n">
-        <v>23888</v>
+        <v>1395</v>
       </c>
     </row>
   </sheetData>
